--- a/Data arranques.xlsx
+++ b/Data arranques.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Planificador02\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{533DD41E-292B-410F-8217-B3D988721FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E465DE5C-BD11-4678-AA7A-F146F051625A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Fecha</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>Chasia tiny</t>
+  </si>
+  <si>
+    <t>Frontal tiny</t>
   </si>
 </sst>
 </file>
@@ -1035,10 +1038,18 @@
       </c>
     </row>
     <row r="33" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="6"/>
+      <c r="A33" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B33" s="4">
+        <v>42</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="6">
+        <v>0.16666666666666666</v>
+      </c>
     </row>
     <row r="34" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
